--- a/Tubex_Oct26.xlsx
+++ b/Tubex_Oct26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_99FFE1A140E506E4384C75B55A3E7472B3CAFBB9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_A807381B9AB5660CE23DEE2D35D29658DB2A87C0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5580,8 +5580,8 @@
     <col min="13" max="13" width="14.7109375" style="90" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" style="90" customWidth="1"/>
     <col min="15" max="15" width="9.5703125" style="90" customWidth="1"/>
-    <col min="16" max="231" width="8.7109375" style="90" customWidth="1"/>
-    <col min="232" max="16384" width="8.7109375" style="90"/>
+    <col min="16" max="232" width="8.7109375" style="90" customWidth="1"/>
+    <col min="233" max="16384" width="8.7109375" style="90"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -51736,14 +51736,14 @@
   </autoFilter>
   <mergeCells count="9">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A23:K23"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A75:K75"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
